--- a/data/monthly/【2025年9月】月次数値.xlsx
+++ b/data/monthly/【2025年9月】月次数値.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="153">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -234,6 +234,270 @@
   </si>
   <si>
     <t>銀座トレーニングラボ</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Dining Bar Lien】...</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】
+＼ドキドキ💓はじめてのスポーツ体験！／...</t>
+  </si>
+  <si>
+    <t>2026-01-02</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Meibuキッズ空手教室】
+＼2〜3歳のお子さまも大歓迎👶✨／...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍町寿司いちもんめ｜福井市大手...</t>
+  </si>
+  <si>
+    <t>2026-07-06</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌸【女性クリニック ラポール】🌸
+すべての世代の女性に、安心と寄り添いを。...</t>
+  </si>
+  <si>
+    <t>2026-04-10</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【髙橋歯科】
+“噛み合わせ”から整える、お口とカラダのトータルケア🪥...</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📍Wild Crepes - ワイルドクレープス
+安い！旨い！多い！🎉...</t>
+  </si>
+  <si>
+    <t>2026-07-13</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍸【bar moon walk 三条木屋町店】🌙...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶【駕町 とくさ】熊本・花畑町駅 徒歩5分...</t>
+  </si>
+  <si>
+    <t>炭焼　猿一</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>島田屋　東苗穂店</t>
+  </si>
+  <si>
+    <t>居ZAKKU　CHENOWA</t>
+  </si>
+  <si>
+    <t>三千段の民宿　幸登里</t>
+  </si>
+  <si>
+    <t>てんぐ屋</t>
+  </si>
+  <si>
+    <t>炭火焼肉友丸</t>
+  </si>
+  <si>
+    <t>旬彩屋　笑味</t>
+  </si>
+  <si>
+    <t>有限会社　大嶋_うまか喰い処 祇園 大しま</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【海鮮と肉料理 ほっかい酒房】🍣🍢✨
+すすきの駅から徒歩3分🚶‍♂️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【🦷アキュラデンタルクリニック🦷】...</t>
+  </si>
+  <si>
+    <t>archived</t>
+  </si>
+  <si>
+    <t>2025-08-19</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【せがわ歯科クリニック】です🦷✨...</t>
+  </si>
+  <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【ORINAS】です🍽️✨...</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【CasualClub青】です🎤✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【Mix Bar Blo】です🍸✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【はんすう】です🍦✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【すし嘉まさ】🍣✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【すし嘉まさ】新しい仲間を募集しています！🍣✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【鮨一花】🍣✨
+豊水すすきの駅から徒歩1分🚶‍♂️🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 新潟県長岡市に佇むカフェ『樹林館』🌳☕️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 「新潟県長岡市に佇むカフェ『樹林館』🌳☕️...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍴肴家 信清🍷...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 家系ラーメン武将家　浅草店
+10月5日にオープンした『家系らーめん...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 「SEA DROP Roast...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍽️【特別な日のご褒美に】...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 和牛焼肉としお
+🥩和牛焼肉の新境地へ— 🥩...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 【駅チカ×喫煙OK×最新機種】🎤✨...</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍜日々“育てる”一杯、ここにあり🔥...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷✨クオリティ高×価格安×lowkeyな接客✨🍴...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨2024年9月20日 NEW OPEN✨
+Hairsalon...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: インプラント治療なら「上志津中央歯科」🌟...</t>
+  </si>
+  <si>
+    <t>recently_completed</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 中洲にあるミュージックカラオケバー！Food持ち込み可🍴🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🔥【香り豊かな炭火焼と多彩な日本酒が楽しめる！】🔥...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: んにちは！【Mont Blanc】です🍸✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟SUNRISEガールズバー｜豊田市山之手🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 株式会社 TechVoice・FRETTA 🍸
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 📢 株式会社 TechVoice・FRETTA スタッフ募集中！ 🍸
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🏡☕canurip Cafe☕🏡
+茨木に佇む韓国風古民家カフェღ...</t>
+  </si>
+  <si>
+    <t>2026-09-27</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍻 鉄板居酒屋こぐま 🔥
+🏡 アットホームな空間で、心もお腹も大満足！...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 至福のひとときを、すすきの 蟹一 で。
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍶 合同会社 大和・北海道の幸とお酒 たかふじ 🐟
+✨...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨ 天ぷら むらやま｜吉祥寺 ✨
+ゆったりとした カウンター席...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 遠心太助 – 新発想の洗浄ツールで塗装コスト削減！ 🌍
+🔹...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍷 pikku onni 🍽️
+🐟 北海道の海の恵み ×...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🥩 焼肉処 縁結び｜鮮度抜群の極上焼肉 🥩...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🎤 カラオケサーカス 調布店 🎪✨
+東京・調布市の音楽オアシス！🌆🎶...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟大林歯科医院｜千葉県美浜区幕張西🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟栄駅から徒歩2分の歯医者【日生歯科診療所】🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟府中市の歯医者【たかすぎ歯科クリニック】🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟かわらもと歯科｜大阪市・吹田市🌟...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🍻【リーズナブルにたくさん食べたいなら「居酒屋一（ichi）」】🍻...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: ✨【国分町に新しい刺激を！】✨
+「Extreme Bar...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌻季節の食材を使った心温まるお料理とお酒🌻...</t>
+  </si>
+  <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌟【焼鳥の真髄、ここにあり】🌟
+「焼鳥酒場...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🌙【川越の夜をおしゃれに楽しむならここ！】🌙
+「AMUSEMENT Bar...</t>
+  </si>
+  <si>
+    <t>Instagram投稿: 🐾✨ Heart Dog ✨🐶
+ドッグカフェ 庵（いおり） OPEN！...</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
   </si>
 </sst>
 </file>
@@ -583,7 +847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y24"/>
+  <dimension ref="A1:Y91"/>
   <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -2153,7 +2417,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2225,6 +2489,4790 @@
       </c>
       <c r="Y24">
         <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F25">
+        <v>137</v>
+      </c>
+      <c r="G25" t="s">
+        <v>39</v>
+      </c>
+      <c r="H25">
+        <v>4569</v>
+      </c>
+      <c r="I25">
+        <v>1.546071</v>
+      </c>
+      <c r="J25">
+        <v>34.992700730000003</v>
+      </c>
+      <c r="K25">
+        <v>160</v>
+      </c>
+      <c r="L25" t="s">
+        <v>30</v>
+      </c>
+      <c r="M25">
+        <v>4794</v>
+      </c>
+      <c r="N25" t="s">
+        <v>74</v>
+      </c>
+      <c r="O25">
+        <v>7064</v>
+      </c>
+      <c r="P25">
+        <v>678.65232200000003</v>
+      </c>
+      <c r="Q25">
+        <v>137</v>
+      </c>
+      <c r="S25">
+        <v>34.992700999999997</v>
+      </c>
+      <c r="T25">
+        <v>1.939411</v>
+      </c>
+      <c r="U25">
+        <v>155</v>
+      </c>
+      <c r="V25">
+        <v>2.1942240000000002</v>
+      </c>
+      <c r="W25">
+        <v>30.929031999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26">
+        <v>6</v>
+      </c>
+      <c r="G26" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26">
+        <v>264</v>
+      </c>
+      <c r="I26">
+        <v>1.0530299999999999</v>
+      </c>
+      <c r="J26">
+        <v>38.666666669999998</v>
+      </c>
+      <c r="K26">
+        <v>160</v>
+      </c>
+      <c r="L26" t="s">
+        <v>30</v>
+      </c>
+      <c r="M26">
+        <v>232</v>
+      </c>
+      <c r="N26" t="s">
+        <v>76</v>
+      </c>
+      <c r="O26">
+        <v>278</v>
+      </c>
+      <c r="P26">
+        <v>834.532374</v>
+      </c>
+      <c r="Q26">
+        <v>6</v>
+      </c>
+      <c r="S26">
+        <v>38.666666999999997</v>
+      </c>
+      <c r="T26">
+        <v>2.1582729999999999</v>
+      </c>
+      <c r="U26">
+        <v>7</v>
+      </c>
+      <c r="V26">
+        <v>2.5179860000000001</v>
+      </c>
+      <c r="W26">
+        <v>33.142856999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" t="s">
+        <v>28</v>
+      </c>
+      <c r="E27" t="s">
+        <v>29</v>
+      </c>
+      <c r="F27">
+        <v>9</v>
+      </c>
+      <c r="G27" t="s">
+        <v>39</v>
+      </c>
+      <c r="H27">
+        <v>292</v>
+      </c>
+      <c r="I27">
+        <v>1.0308219999999999</v>
+      </c>
+      <c r="J27">
+        <v>23.444444440000002</v>
+      </c>
+      <c r="K27">
+        <v>160</v>
+      </c>
+      <c r="L27" t="s">
+        <v>30</v>
+      </c>
+      <c r="M27">
+        <v>211</v>
+      </c>
+      <c r="N27" t="s">
+        <v>76</v>
+      </c>
+      <c r="O27">
+        <v>301</v>
+      </c>
+      <c r="P27">
+        <v>700.99667799999997</v>
+      </c>
+      <c r="Q27">
+        <v>9</v>
+      </c>
+      <c r="S27">
+        <v>23.444444000000001</v>
+      </c>
+      <c r="T27">
+        <v>2.9900329999999999</v>
+      </c>
+      <c r="U27">
+        <v>13</v>
+      </c>
+      <c r="V27">
+        <v>4.318937</v>
+      </c>
+      <c r="W27">
+        <v>16.230768999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C28" t="s">
+        <v>78</v>
+      </c>
+      <c r="D28" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F28">
+        <v>120</v>
+      </c>
+      <c r="G28" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28">
+        <v>2124</v>
+      </c>
+      <c r="I28">
+        <v>1.4016010000000001</v>
+      </c>
+      <c r="J28">
+        <v>40.083333330000002</v>
+      </c>
+      <c r="K28">
+        <v>160</v>
+      </c>
+      <c r="L28" t="s">
+        <v>30</v>
+      </c>
+      <c r="M28">
+        <v>4810</v>
+      </c>
+      <c r="N28" t="s">
+        <v>79</v>
+      </c>
+      <c r="O28">
+        <v>2977</v>
+      </c>
+      <c r="P28">
+        <v>1615.7205240000001</v>
+      </c>
+      <c r="Q28">
+        <v>120</v>
+      </c>
+      <c r="S28">
+        <v>40.083333000000003</v>
+      </c>
+      <c r="T28">
+        <v>4.0309039999999996</v>
+      </c>
+      <c r="U28">
+        <v>122</v>
+      </c>
+      <c r="V28">
+        <v>4.0980850000000002</v>
+      </c>
+      <c r="W28">
+        <v>39.426229999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E29" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29">
+        <v>100</v>
+      </c>
+      <c r="G29" t="s">
+        <v>39</v>
+      </c>
+      <c r="H29">
+        <v>2659</v>
+      </c>
+      <c r="I29">
+        <v>1.7326060000000001</v>
+      </c>
+      <c r="J29">
+        <v>48.18</v>
+      </c>
+      <c r="K29">
+        <v>160</v>
+      </c>
+      <c r="L29" t="s">
+        <v>30</v>
+      </c>
+      <c r="M29">
+        <v>4818</v>
+      </c>
+      <c r="N29" t="s">
+        <v>81</v>
+      </c>
+      <c r="O29">
+        <v>4607</v>
+      </c>
+      <c r="P29">
+        <v>1045.7998700000001</v>
+      </c>
+      <c r="Q29">
+        <v>100</v>
+      </c>
+      <c r="S29">
+        <v>48.18</v>
+      </c>
+      <c r="T29">
+        <v>2.1706099999999999</v>
+      </c>
+      <c r="U29">
+        <v>112</v>
+      </c>
+      <c r="V29">
+        <v>2.4310830000000001</v>
+      </c>
+      <c r="W29">
+        <v>43.017856999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" t="s">
+        <v>82</v>
+      </c>
+      <c r="D30" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" t="s">
+        <v>29</v>
+      </c>
+      <c r="F30">
+        <v>111</v>
+      </c>
+      <c r="G30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H30">
+        <v>2685</v>
+      </c>
+      <c r="I30">
+        <v>1.335196</v>
+      </c>
+      <c r="J30">
+        <v>42.846846849999999</v>
+      </c>
+      <c r="K30">
+        <v>160</v>
+      </c>
+      <c r="L30" t="s">
+        <v>30</v>
+      </c>
+      <c r="M30">
+        <v>4756</v>
+      </c>
+      <c r="N30" t="s">
+        <v>83</v>
+      </c>
+      <c r="O30">
+        <v>3585</v>
+      </c>
+      <c r="P30">
+        <v>1326.6387729999999</v>
+      </c>
+      <c r="Q30">
+        <v>111</v>
+      </c>
+      <c r="S30">
+        <v>42.846846999999997</v>
+      </c>
+      <c r="T30">
+        <v>3.0962339999999999</v>
+      </c>
+      <c r="U30">
+        <v>122</v>
+      </c>
+      <c r="V30">
+        <v>3.4030680000000002</v>
+      </c>
+      <c r="W30">
+        <v>38.983606999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E31" t="s">
+        <v>29</v>
+      </c>
+      <c r="F31">
+        <v>211</v>
+      </c>
+      <c r="G31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H31">
+        <v>4902</v>
+      </c>
+      <c r="I31">
+        <v>1.4016729999999999</v>
+      </c>
+      <c r="J31">
+        <v>22.815165879999999</v>
+      </c>
+      <c r="K31">
+        <v>160</v>
+      </c>
+      <c r="L31" t="s">
+        <v>30</v>
+      </c>
+      <c r="M31">
+        <v>4814</v>
+      </c>
+      <c r="N31" t="s">
+        <v>85</v>
+      </c>
+      <c r="O31">
+        <v>6871</v>
+      </c>
+      <c r="P31">
+        <v>700.62581899999998</v>
+      </c>
+      <c r="Q31">
+        <v>211</v>
+      </c>
+      <c r="S31">
+        <v>22.815166000000001</v>
+      </c>
+      <c r="T31">
+        <v>3.070878</v>
+      </c>
+      <c r="U31">
+        <v>225</v>
+      </c>
+      <c r="V31">
+        <v>3.2746330000000001</v>
+      </c>
+      <c r="W31">
+        <v>21.395555999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" t="s">
+        <v>86</v>
+      </c>
+      <c r="D32" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" t="s">
+        <v>29</v>
+      </c>
+      <c r="F32">
+        <v>88</v>
+      </c>
+      <c r="G32" t="s">
+        <v>39</v>
+      </c>
+      <c r="H32">
+        <v>1964</v>
+      </c>
+      <c r="I32">
+        <v>1.428717</v>
+      </c>
+      <c r="J32">
+        <v>55.340909089999997</v>
+      </c>
+      <c r="K32">
+        <v>160</v>
+      </c>
+      <c r="L32" t="s">
+        <v>30</v>
+      </c>
+      <c r="M32">
+        <v>4870</v>
+      </c>
+      <c r="N32" t="s">
+        <v>85</v>
+      </c>
+      <c r="O32">
+        <v>2806</v>
+      </c>
+      <c r="P32">
+        <v>1735.5666430000001</v>
+      </c>
+      <c r="Q32">
+        <v>88</v>
+      </c>
+      <c r="S32">
+        <v>55.340909000000003</v>
+      </c>
+      <c r="T32">
+        <v>3.1361370000000002</v>
+      </c>
+      <c r="U32">
+        <v>102</v>
+      </c>
+      <c r="V32">
+        <v>3.635068</v>
+      </c>
+      <c r="W32">
+        <v>47.745097999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" t="s">
+        <v>87</v>
+      </c>
+      <c r="D33" t="s">
+        <v>38</v>
+      </c>
+      <c r="E33" t="s">
+        <v>29</v>
+      </c>
+      <c r="F33">
+        <v>299</v>
+      </c>
+      <c r="G33" t="s">
+        <v>39</v>
+      </c>
+      <c r="H33">
+        <v>3834</v>
+      </c>
+      <c r="I33">
+        <v>1.6379760000000001</v>
+      </c>
+      <c r="J33">
+        <v>16.096989969999999</v>
+      </c>
+      <c r="K33">
+        <v>160</v>
+      </c>
+      <c r="L33" t="s">
+        <v>30</v>
+      </c>
+      <c r="M33">
+        <v>4813</v>
+      </c>
+      <c r="N33" t="s">
+        <v>85</v>
+      </c>
+      <c r="O33">
+        <v>6280</v>
+      </c>
+      <c r="P33">
+        <v>766.40127399999994</v>
+      </c>
+      <c r="Q33">
+        <v>299</v>
+      </c>
+      <c r="S33">
+        <v>16.096990000000002</v>
+      </c>
+      <c r="T33">
+        <v>4.7611470000000002</v>
+      </c>
+      <c r="U33">
+        <v>330</v>
+      </c>
+      <c r="V33">
+        <v>5.2547769999999998</v>
+      </c>
+      <c r="W33">
+        <v>14.584847999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>88</v>
+      </c>
+      <c r="D34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34">
+        <v>371</v>
+      </c>
+      <c r="G34" t="s">
+        <v>39</v>
+      </c>
+      <c r="H34">
+        <v>5980</v>
+      </c>
+      <c r="I34">
+        <v>1.5396319999999999</v>
+      </c>
+      <c r="J34">
+        <v>14.719676550000001</v>
+      </c>
+      <c r="K34" t="s">
+        <v>34</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>5461</v>
+      </c>
+      <c r="N34" t="s">
+        <v>89</v>
+      </c>
+      <c r="O34">
+        <v>9207</v>
+      </c>
+      <c r="P34">
+        <v>593.13565800000003</v>
+      </c>
+      <c r="Q34">
+        <v>371</v>
+      </c>
+      <c r="S34">
+        <v>14.719677000000001</v>
+      </c>
+      <c r="T34">
+        <v>4.0295430000000003</v>
+      </c>
+      <c r="U34">
+        <v>411</v>
+      </c>
+      <c r="V34">
+        <v>4.4639949999999997</v>
+      </c>
+      <c r="W34">
+        <v>13.287105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" t="s">
+        <v>38</v>
+      </c>
+      <c r="E35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35">
+        <v>382</v>
+      </c>
+      <c r="G35" t="s">
+        <v>39</v>
+      </c>
+      <c r="H35">
+        <v>7457</v>
+      </c>
+      <c r="I35">
+        <v>1.433284</v>
+      </c>
+      <c r="J35">
+        <v>13.926701570000001</v>
+      </c>
+      <c r="K35" t="s">
+        <v>34</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>5320</v>
+      </c>
+      <c r="N35" t="s">
+        <v>89</v>
+      </c>
+      <c r="O35">
+        <v>10688</v>
+      </c>
+      <c r="P35">
+        <v>497.75449099999997</v>
+      </c>
+      <c r="Q35">
+        <v>382</v>
+      </c>
+      <c r="S35">
+        <v>13.926702000000001</v>
+      </c>
+      <c r="T35">
+        <v>3.5741019999999999</v>
+      </c>
+      <c r="U35">
+        <v>397</v>
+      </c>
+      <c r="V35">
+        <v>3.7144460000000001</v>
+      </c>
+      <c r="W35">
+        <v>13.400504</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" t="s">
+        <v>38</v>
+      </c>
+      <c r="E36" t="s">
+        <v>29</v>
+      </c>
+      <c r="F36">
+        <v>129</v>
+      </c>
+      <c r="G36" t="s">
+        <v>39</v>
+      </c>
+      <c r="H36">
+        <v>4357</v>
+      </c>
+      <c r="I36">
+        <v>1.6922189999999999</v>
+      </c>
+      <c r="J36">
+        <v>45.565891469999997</v>
+      </c>
+      <c r="K36" t="s">
+        <v>34</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>5878</v>
+      </c>
+      <c r="N36" t="s">
+        <v>35</v>
+      </c>
+      <c r="O36">
+        <v>7373</v>
+      </c>
+      <c r="P36">
+        <v>797.23314800000003</v>
+      </c>
+      <c r="Q36">
+        <v>129</v>
+      </c>
+      <c r="S36">
+        <v>45.565891000000001</v>
+      </c>
+      <c r="T36">
+        <v>1.749627</v>
+      </c>
+      <c r="U36">
+        <v>189</v>
+      </c>
+      <c r="V36">
+        <v>2.5634070000000002</v>
+      </c>
+      <c r="W36">
+        <v>31.100529000000002</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>25</v>
+      </c>
+      <c r="B37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" t="s">
+        <v>92</v>
+      </c>
+      <c r="D37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E37" t="s">
+        <v>29</v>
+      </c>
+      <c r="F37">
+        <v>148</v>
+      </c>
+      <c r="G37" t="s">
+        <v>39</v>
+      </c>
+      <c r="H37">
+        <v>4157</v>
+      </c>
+      <c r="I37">
+        <v>1.5419769999999999</v>
+      </c>
+      <c r="J37">
+        <v>40.5</v>
+      </c>
+      <c r="K37" t="s">
+        <v>34</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>5994</v>
+      </c>
+      <c r="N37" t="s">
+        <v>89</v>
+      </c>
+      <c r="O37">
+        <v>6410</v>
+      </c>
+      <c r="P37">
+        <v>935.101404</v>
+      </c>
+      <c r="Q37">
+        <v>148</v>
+      </c>
+      <c r="S37">
+        <v>40.5</v>
+      </c>
+      <c r="T37">
+        <v>2.3088920000000002</v>
+      </c>
+      <c r="U37">
+        <v>159</v>
+      </c>
+      <c r="V37">
+        <v>2.480499</v>
+      </c>
+      <c r="W37">
+        <v>37.698112999999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" t="s">
+        <v>93</v>
+      </c>
+      <c r="D38" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" t="s">
+        <v>29</v>
+      </c>
+      <c r="F38">
+        <v>487</v>
+      </c>
+      <c r="G38" t="s">
+        <v>39</v>
+      </c>
+      <c r="H38">
+        <v>6339</v>
+      </c>
+      <c r="I38">
+        <v>1.446758</v>
+      </c>
+      <c r="J38">
+        <v>11.28542094</v>
+      </c>
+      <c r="K38" t="s">
+        <v>34</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>5496</v>
+      </c>
+      <c r="N38" t="s">
+        <v>35</v>
+      </c>
+      <c r="O38">
+        <v>9171</v>
+      </c>
+      <c r="P38">
+        <v>599.28034000000002</v>
+      </c>
+      <c r="Q38">
+        <v>487</v>
+      </c>
+      <c r="S38">
+        <v>11.285420999999999</v>
+      </c>
+      <c r="T38">
+        <v>5.3102169999999997</v>
+      </c>
+      <c r="U38">
+        <v>543</v>
+      </c>
+      <c r="V38">
+        <v>5.9208369999999997</v>
+      </c>
+      <c r="W38">
+        <v>10.121547</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B39" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39">
+        <v>194</v>
+      </c>
+      <c r="G39" t="s">
+        <v>39</v>
+      </c>
+      <c r="H39">
+        <v>5692</v>
+      </c>
+      <c r="I39">
+        <v>1.5643009999999999</v>
+      </c>
+      <c r="J39">
+        <v>28.726804120000001</v>
+      </c>
+      <c r="K39" t="s">
+        <v>34</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>5573</v>
+      </c>
+      <c r="N39" t="s">
+        <v>35</v>
+      </c>
+      <c r="O39">
+        <v>8904</v>
+      </c>
+      <c r="P39">
+        <v>625.89847299999997</v>
+      </c>
+      <c r="Q39">
+        <v>194</v>
+      </c>
+      <c r="S39">
+        <v>28.726804000000001</v>
+      </c>
+      <c r="T39">
+        <v>2.1787960000000002</v>
+      </c>
+      <c r="U39">
+        <v>228</v>
+      </c>
+      <c r="V39">
+        <v>2.5606469999999999</v>
+      </c>
+      <c r="W39">
+        <v>24.442982000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" t="s">
+        <v>95</v>
+      </c>
+      <c r="D40" t="s">
+        <v>38</v>
+      </c>
+      <c r="E40" t="s">
+        <v>29</v>
+      </c>
+      <c r="F40">
+        <v>224</v>
+      </c>
+      <c r="G40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H40">
+        <v>4275</v>
+      </c>
+      <c r="I40">
+        <v>1.7700579999999999</v>
+      </c>
+      <c r="J40">
+        <v>25.758928569999998</v>
+      </c>
+      <c r="K40" t="s">
+        <v>34</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>5770</v>
+      </c>
+      <c r="N40" t="s">
+        <v>35</v>
+      </c>
+      <c r="O40">
+        <v>7567</v>
+      </c>
+      <c r="P40">
+        <v>762.52147500000001</v>
+      </c>
+      <c r="Q40">
+        <v>224</v>
+      </c>
+      <c r="S40">
+        <v>25.758928999999998</v>
+      </c>
+      <c r="T40">
+        <v>2.9602219999999999</v>
+      </c>
+      <c r="U40">
+        <v>280</v>
+      </c>
+      <c r="V40">
+        <v>3.700278</v>
+      </c>
+      <c r="W40">
+        <v>20.607143000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41">
+        <v>325</v>
+      </c>
+      <c r="G41" t="s">
+        <v>39</v>
+      </c>
+      <c r="H41">
+        <v>5510</v>
+      </c>
+      <c r="I41">
+        <v>1.461525</v>
+      </c>
+      <c r="J41">
+        <v>17.729230770000001</v>
+      </c>
+      <c r="K41" t="s">
+        <v>34</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>5762</v>
+      </c>
+      <c r="N41" t="s">
+        <v>68</v>
+      </c>
+      <c r="O41">
+        <v>8053</v>
+      </c>
+      <c r="P41">
+        <v>715.50974799999995</v>
+      </c>
+      <c r="Q41">
+        <v>325</v>
+      </c>
+      <c r="S41">
+        <v>17.729230999999999</v>
+      </c>
+      <c r="T41">
+        <v>4.0357630000000002</v>
+      </c>
+      <c r="U41">
+        <v>346</v>
+      </c>
+      <c r="V41">
+        <v>4.2965350000000004</v>
+      </c>
+      <c r="W41">
+        <v>16.653179000000002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C42" t="s">
+        <v>97</v>
+      </c>
+      <c r="D42" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42">
+        <v>289</v>
+      </c>
+      <c r="G42" t="s">
+        <v>39</v>
+      </c>
+      <c r="H42">
+        <v>4349</v>
+      </c>
+      <c r="I42">
+        <v>1.4835590000000001</v>
+      </c>
+      <c r="J42">
+        <v>16.70242215</v>
+      </c>
+      <c r="K42">
+        <v>160</v>
+      </c>
+      <c r="L42" t="s">
+        <v>30</v>
+      </c>
+      <c r="M42">
+        <v>4827</v>
+      </c>
+      <c r="N42" t="s">
+        <v>57</v>
+      </c>
+      <c r="O42">
+        <v>6452</v>
+      </c>
+      <c r="P42">
+        <v>748.14011200000004</v>
+      </c>
+      <c r="Q42">
+        <v>289</v>
+      </c>
+      <c r="S42">
+        <v>16.702421999999999</v>
+      </c>
+      <c r="T42">
+        <v>4.4792310000000004</v>
+      </c>
+      <c r="U42">
+        <v>326</v>
+      </c>
+      <c r="V42">
+        <v>5.0526970000000002</v>
+      </c>
+      <c r="W42">
+        <v>14.806748000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>26</v>
+      </c>
+      <c r="C43" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43" t="s">
+        <v>99</v>
+      </c>
+      <c r="E43" t="s">
+        <v>29</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>650</v>
+      </c>
+      <c r="L43" t="s">
+        <v>30</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43" t="s">
+        <v>100</v>
+      </c>
+      <c r="O43">
+        <v>0</v>
+      </c>
+      <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" t="s">
+        <v>101</v>
+      </c>
+      <c r="D44" t="s">
+        <v>38</v>
+      </c>
+      <c r="E44" t="s">
+        <v>29</v>
+      </c>
+      <c r="F44">
+        <v>111</v>
+      </c>
+      <c r="G44" t="s">
+        <v>39</v>
+      </c>
+      <c r="H44">
+        <v>4764</v>
+      </c>
+      <c r="I44">
+        <v>1.3570530000000001</v>
+      </c>
+      <c r="J44">
+        <v>43.306306309999997</v>
+      </c>
+      <c r="K44">
+        <v>160</v>
+      </c>
+      <c r="L44" t="s">
+        <v>30</v>
+      </c>
+      <c r="M44">
+        <v>4807</v>
+      </c>
+      <c r="N44" t="s">
+        <v>102</v>
+      </c>
+      <c r="O44">
+        <v>6465</v>
+      </c>
+      <c r="P44">
+        <v>743.54214999999999</v>
+      </c>
+      <c r="Q44">
+        <v>111</v>
+      </c>
+      <c r="S44">
+        <v>43.306305999999999</v>
+      </c>
+      <c r="T44">
+        <v>1.7169369999999999</v>
+      </c>
+      <c r="U44">
+        <v>133</v>
+      </c>
+      <c r="V44">
+        <v>2.0572309999999998</v>
+      </c>
+      <c r="W44">
+        <v>36.142856999999999</v>
+      </c>
+      <c r="X44">
+        <v>89</v>
+      </c>
+      <c r="Y44">
+        <v>54.011235999999997</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>25</v>
+      </c>
+      <c r="B45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" t="s">
+        <v>103</v>
+      </c>
+      <c r="D45" t="s">
+        <v>38</v>
+      </c>
+      <c r="E45" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45">
+        <v>206</v>
+      </c>
+      <c r="G45" t="s">
+        <v>39</v>
+      </c>
+      <c r="H45">
+        <v>3739</v>
+      </c>
+      <c r="I45">
+        <v>1.552287</v>
+      </c>
+      <c r="J45">
+        <v>22.747572819999998</v>
+      </c>
+      <c r="K45">
+        <v>160</v>
+      </c>
+      <c r="L45" t="s">
+        <v>30</v>
+      </c>
+      <c r="M45">
+        <v>4686</v>
+      </c>
+      <c r="N45" t="s">
+        <v>104</v>
+      </c>
+      <c r="O45">
+        <v>5804</v>
+      </c>
+      <c r="P45">
+        <v>807.37422500000002</v>
+      </c>
+      <c r="Q45">
+        <v>206</v>
+      </c>
+      <c r="S45">
+        <v>22.747572999999999</v>
+      </c>
+      <c r="T45">
+        <v>3.5492759999999999</v>
+      </c>
+      <c r="U45">
+        <v>236</v>
+      </c>
+      <c r="V45">
+        <v>4.0661610000000001</v>
+      </c>
+      <c r="W45">
+        <v>19.855931999999999</v>
+      </c>
+      <c r="X45">
+        <v>182</v>
+      </c>
+      <c r="Y45">
+        <v>25.747253000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>25</v>
+      </c>
+      <c r="B46" t="s">
+        <v>26</v>
+      </c>
+      <c r="C46" t="s">
+        <v>105</v>
+      </c>
+      <c r="D46" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F46">
+        <v>224</v>
+      </c>
+      <c r="G46" t="s">
+        <v>39</v>
+      </c>
+      <c r="H46">
+        <v>4514</v>
+      </c>
+      <c r="I46">
+        <v>1.572441</v>
+      </c>
+      <c r="J46">
+        <v>20.928571430000002</v>
+      </c>
+      <c r="K46">
+        <v>160</v>
+      </c>
+      <c r="L46" t="s">
+        <v>30</v>
+      </c>
+      <c r="M46">
+        <v>4688</v>
+      </c>
+      <c r="N46" t="s">
+        <v>104</v>
+      </c>
+      <c r="O46">
+        <v>7098</v>
+      </c>
+      <c r="P46">
+        <v>660.46773700000006</v>
+      </c>
+      <c r="Q46">
+        <v>224</v>
+      </c>
+      <c r="S46">
+        <v>20.928571000000002</v>
+      </c>
+      <c r="T46">
+        <v>3.1558190000000002</v>
+      </c>
+      <c r="U46">
+        <v>241</v>
+      </c>
+      <c r="V46">
+        <v>3.3953229999999999</v>
+      </c>
+      <c r="W46">
+        <v>19.452282</v>
+      </c>
+      <c r="X46">
+        <v>203</v>
+      </c>
+      <c r="Y46">
+        <v>23.093596000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" t="s">
+        <v>38</v>
+      </c>
+      <c r="E47" t="s">
+        <v>29</v>
+      </c>
+      <c r="F47">
+        <v>306</v>
+      </c>
+      <c r="G47" t="s">
+        <v>39</v>
+      </c>
+      <c r="H47">
+        <v>3471</v>
+      </c>
+      <c r="I47">
+        <v>2.1673870000000002</v>
+      </c>
+      <c r="J47">
+        <v>15.222222220000001</v>
+      </c>
+      <c r="K47">
+        <v>160</v>
+      </c>
+      <c r="L47" t="s">
+        <v>30</v>
+      </c>
+      <c r="M47">
+        <v>4658</v>
+      </c>
+      <c r="N47" t="s">
+        <v>104</v>
+      </c>
+      <c r="O47">
+        <v>7523</v>
+      </c>
+      <c r="P47">
+        <v>619.16788499999996</v>
+      </c>
+      <c r="Q47">
+        <v>306</v>
+      </c>
+      <c r="S47">
+        <v>15.222222</v>
+      </c>
+      <c r="T47">
+        <v>4.067526</v>
+      </c>
+      <c r="U47">
+        <v>425</v>
+      </c>
+      <c r="V47">
+        <v>5.6493419999999999</v>
+      </c>
+      <c r="W47">
+        <v>10.96</v>
+      </c>
+      <c r="X47">
+        <v>75</v>
+      </c>
+      <c r="Y47">
+        <v>62.106667000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>25</v>
+      </c>
+      <c r="B48" t="s">
+        <v>26</v>
+      </c>
+      <c r="C48" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" t="s">
+        <v>38</v>
+      </c>
+      <c r="E48" t="s">
+        <v>29</v>
+      </c>
+      <c r="F48">
+        <v>134</v>
+      </c>
+      <c r="G48" t="s">
+        <v>39</v>
+      </c>
+      <c r="H48">
+        <v>4227</v>
+      </c>
+      <c r="I48">
+        <v>1.6281049999999999</v>
+      </c>
+      <c r="J48">
+        <v>35.268656720000003</v>
+      </c>
+      <c r="K48">
+        <v>160</v>
+      </c>
+      <c r="L48" t="s">
+        <v>30</v>
+      </c>
+      <c r="M48">
+        <v>4726</v>
+      </c>
+      <c r="N48" t="s">
+        <v>104</v>
+      </c>
+      <c r="O48">
+        <v>6882</v>
+      </c>
+      <c r="P48">
+        <v>686.718977</v>
+      </c>
+      <c r="Q48">
+        <v>134</v>
+      </c>
+      <c r="S48">
+        <v>35.268656999999997</v>
+      </c>
+      <c r="T48">
+        <v>1.9471080000000001</v>
+      </c>
+      <c r="U48">
+        <v>172</v>
+      </c>
+      <c r="V48">
+        <v>2.4992730000000001</v>
+      </c>
+      <c r="W48">
+        <v>27.476744</v>
+      </c>
+      <c r="X48">
+        <v>43</v>
+      </c>
+      <c r="Y48">
+        <v>109.906977</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" t="s">
+        <v>26</v>
+      </c>
+      <c r="C49" t="s">
+        <v>108</v>
+      </c>
+      <c r="D49" t="s">
+        <v>28</v>
+      </c>
+      <c r="E49" t="s">
+        <v>29</v>
+      </c>
+      <c r="F49">
+        <v>44</v>
+      </c>
+      <c r="G49" t="s">
+        <v>39</v>
+      </c>
+      <c r="H49">
+        <v>631</v>
+      </c>
+      <c r="I49">
+        <v>1.1553089999999999</v>
+      </c>
+      <c r="J49">
+        <v>9.4545454499999995</v>
+      </c>
+      <c r="K49">
+        <v>160</v>
+      </c>
+      <c r="L49" t="s">
+        <v>30</v>
+      </c>
+      <c r="M49">
+        <v>416</v>
+      </c>
+      <c r="N49" t="s">
+        <v>104</v>
+      </c>
+      <c r="O49">
+        <v>729</v>
+      </c>
+      <c r="P49">
+        <v>570.64471900000001</v>
+      </c>
+      <c r="Q49">
+        <v>44</v>
+      </c>
+      <c r="S49">
+        <v>9.4545449999999995</v>
+      </c>
+      <c r="T49">
+        <v>6.0356649999999998</v>
+      </c>
+      <c r="U49">
+        <v>48</v>
+      </c>
+      <c r="V49">
+        <v>6.5843619999999996</v>
+      </c>
+      <c r="W49">
+        <v>8.6666670000000003</v>
+      </c>
+      <c r="X49">
+        <v>39</v>
+      </c>
+      <c r="Y49">
+        <v>10.666667</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>25</v>
+      </c>
+      <c r="B50" t="s">
+        <v>26</v>
+      </c>
+      <c r="C50" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" t="s">
+        <v>28</v>
+      </c>
+      <c r="E50" t="s">
+        <v>29</v>
+      </c>
+      <c r="F50">
+        <v>8</v>
+      </c>
+      <c r="G50" t="s">
+        <v>39</v>
+      </c>
+      <c r="H50">
+        <v>463</v>
+      </c>
+      <c r="I50">
+        <v>1.0691139999999999</v>
+      </c>
+      <c r="J50">
+        <v>48</v>
+      </c>
+      <c r="K50">
+        <v>160</v>
+      </c>
+      <c r="L50" t="s">
+        <v>30</v>
+      </c>
+      <c r="M50">
+        <v>384</v>
+      </c>
+      <c r="N50" t="s">
+        <v>104</v>
+      </c>
+      <c r="O50">
+        <v>495</v>
+      </c>
+      <c r="P50">
+        <v>775.75757599999997</v>
+      </c>
+      <c r="Q50">
+        <v>8</v>
+      </c>
+      <c r="S50">
+        <v>48</v>
+      </c>
+      <c r="T50">
+        <v>1.6161620000000001</v>
+      </c>
+      <c r="U50">
+        <v>9</v>
+      </c>
+      <c r="V50">
+        <v>1.818182</v>
+      </c>
+      <c r="W50">
+        <v>42.666666999999997</v>
+      </c>
+      <c r="X50">
+        <v>6</v>
+      </c>
+      <c r="Y50">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>25</v>
+      </c>
+      <c r="B51" t="s">
+        <v>26</v>
+      </c>
+      <c r="C51" t="s">
+        <v>110</v>
+      </c>
+      <c r="D51" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51">
+        <v>62</v>
+      </c>
+      <c r="G51" t="s">
+        <v>39</v>
+      </c>
+      <c r="H51">
+        <v>1154</v>
+      </c>
+      <c r="I51">
+        <v>1.129983</v>
+      </c>
+      <c r="J51">
+        <v>13.48387097</v>
+      </c>
+      <c r="K51">
+        <v>320</v>
+      </c>
+      <c r="L51" t="s">
+        <v>30</v>
+      </c>
+      <c r="M51">
+        <v>836</v>
+      </c>
+      <c r="N51" t="s">
+        <v>104</v>
+      </c>
+      <c r="O51">
+        <v>1304</v>
+      </c>
+      <c r="P51">
+        <v>641.10429399999998</v>
+      </c>
+      <c r="Q51">
+        <v>62</v>
+      </c>
+      <c r="S51">
+        <v>13.483871000000001</v>
+      </c>
+      <c r="T51">
+        <v>4.7546010000000001</v>
+      </c>
+      <c r="U51">
+        <v>67</v>
+      </c>
+      <c r="V51">
+        <v>5.1380369999999997</v>
+      </c>
+      <c r="W51">
+        <v>12.477612000000001</v>
+      </c>
+      <c r="X51">
+        <v>55</v>
+      </c>
+      <c r="Y51">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>25</v>
+      </c>
+      <c r="B52" t="s">
+        <v>26</v>
+      </c>
+      <c r="C52" t="s">
+        <v>111</v>
+      </c>
+      <c r="D52" t="s">
+        <v>38</v>
+      </c>
+      <c r="E52" t="s">
+        <v>29</v>
+      </c>
+      <c r="F52">
+        <v>429</v>
+      </c>
+      <c r="G52" t="s">
+        <v>39</v>
+      </c>
+      <c r="H52">
+        <v>5849</v>
+      </c>
+      <c r="I52">
+        <v>1.6204480000000001</v>
+      </c>
+      <c r="J52">
+        <v>10.883449880000001</v>
+      </c>
+      <c r="K52">
+        <v>160</v>
+      </c>
+      <c r="L52" t="s">
+        <v>30</v>
+      </c>
+      <c r="M52">
+        <v>4669</v>
+      </c>
+      <c r="N52" t="s">
+        <v>104</v>
+      </c>
+      <c r="O52">
+        <v>9478</v>
+      </c>
+      <c r="P52">
+        <v>492.61447600000002</v>
+      </c>
+      <c r="Q52">
+        <v>429</v>
+      </c>
+      <c r="S52">
+        <v>10.88345</v>
+      </c>
+      <c r="T52">
+        <v>4.5262710000000004</v>
+      </c>
+      <c r="U52">
+        <v>512</v>
+      </c>
+      <c r="V52">
+        <v>5.4019839999999997</v>
+      </c>
+      <c r="W52">
+        <v>9.1191410000000008</v>
+      </c>
+      <c r="X52">
+        <v>385</v>
+      </c>
+      <c r="Y52">
+        <v>12.127273000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" t="s">
+        <v>112</v>
+      </c>
+      <c r="D53" t="s">
+        <v>38</v>
+      </c>
+      <c r="E53" t="s">
+        <v>29</v>
+      </c>
+      <c r="F53">
+        <v>379</v>
+      </c>
+      <c r="G53" t="s">
+        <v>39</v>
+      </c>
+      <c r="H53">
+        <v>6756</v>
+      </c>
+      <c r="I53">
+        <v>1.3673770000000001</v>
+      </c>
+      <c r="J53">
+        <v>12.34300792</v>
+      </c>
+      <c r="K53">
+        <v>160</v>
+      </c>
+      <c r="L53" t="s">
+        <v>30</v>
+      </c>
+      <c r="M53">
+        <v>4678</v>
+      </c>
+      <c r="N53" t="s">
+        <v>104</v>
+      </c>
+      <c r="O53">
+        <v>9238</v>
+      </c>
+      <c r="P53">
+        <v>506.386664</v>
+      </c>
+      <c r="Q53">
+        <v>379</v>
+      </c>
+      <c r="S53">
+        <v>12.343007999999999</v>
+      </c>
+      <c r="T53">
+        <v>4.1026199999999999</v>
+      </c>
+      <c r="U53">
+        <v>482</v>
+      </c>
+      <c r="V53">
+        <v>5.2175799999999999</v>
+      </c>
+      <c r="W53">
+        <v>9.7053940000000001</v>
+      </c>
+      <c r="X53">
+        <v>348</v>
+      </c>
+      <c r="Y53">
+        <v>13.442529</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" t="s">
+        <v>26</v>
+      </c>
+      <c r="C54" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" t="s">
+        <v>38</v>
+      </c>
+      <c r="E54" t="s">
+        <v>29</v>
+      </c>
+      <c r="F54">
+        <v>103</v>
+      </c>
+      <c r="G54" t="s">
+        <v>39</v>
+      </c>
+      <c r="H54">
+        <v>3129</v>
+      </c>
+      <c r="I54">
+        <v>1.3518699999999999</v>
+      </c>
+      <c r="J54">
+        <v>45.378640779999998</v>
+      </c>
+      <c r="K54">
+        <v>160</v>
+      </c>
+      <c r="L54" t="s">
+        <v>30</v>
+      </c>
+      <c r="M54">
+        <v>4674</v>
+      </c>
+      <c r="N54" t="s">
+        <v>104</v>
+      </c>
+      <c r="O54">
+        <v>4230</v>
+      </c>
+      <c r="P54">
+        <v>1104.9645390000001</v>
+      </c>
+      <c r="Q54">
+        <v>103</v>
+      </c>
+      <c r="S54">
+        <v>45.378641000000002</v>
+      </c>
+      <c r="T54">
+        <v>2.4349880000000002</v>
+      </c>
+      <c r="U54">
+        <v>105</v>
+      </c>
+      <c r="V54">
+        <v>2.4822700000000002</v>
+      </c>
+      <c r="W54">
+        <v>44.514285999999998</v>
+      </c>
+      <c r="X54">
+        <v>89</v>
+      </c>
+      <c r="Y54">
+        <v>52.516854000000002</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" t="s">
+        <v>26</v>
+      </c>
+      <c r="C55" t="s">
+        <v>114</v>
+      </c>
+      <c r="D55" t="s">
+        <v>38</v>
+      </c>
+      <c r="E55" t="s">
+        <v>29</v>
+      </c>
+      <c r="F55">
+        <v>929</v>
+      </c>
+      <c r="G55" t="s">
+        <v>39</v>
+      </c>
+      <c r="H55">
+        <v>10782</v>
+      </c>
+      <c r="I55">
+        <v>1.220275</v>
+      </c>
+      <c r="J55">
+        <v>5.0086114100000003</v>
+      </c>
+      <c r="K55">
+        <v>160</v>
+      </c>
+      <c r="L55" t="s">
+        <v>30</v>
+      </c>
+      <c r="M55">
+        <v>4653</v>
+      </c>
+      <c r="N55" t="s">
+        <v>104</v>
+      </c>
+      <c r="O55">
+        <v>13157</v>
+      </c>
+      <c r="P55">
+        <v>353.65204799999998</v>
+      </c>
+      <c r="Q55">
+        <v>929</v>
+      </c>
+      <c r="S55">
+        <v>5.0086110000000001</v>
+      </c>
+      <c r="T55">
+        <v>7.06088</v>
+      </c>
+      <c r="U55">
+        <v>1028</v>
+      </c>
+      <c r="V55">
+        <v>7.8133309999999998</v>
+      </c>
+      <c r="W55">
+        <v>4.5262650000000004</v>
+      </c>
+      <c r="X55">
+        <v>831</v>
+      </c>
+      <c r="Y55">
+        <v>5.599278</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" t="s">
+        <v>26</v>
+      </c>
+      <c r="C56" t="s">
+        <v>115</v>
+      </c>
+      <c r="D56" t="s">
+        <v>28</v>
+      </c>
+      <c r="E56" t="s">
+        <v>29</v>
+      </c>
+      <c r="F56">
+        <v>412</v>
+      </c>
+      <c r="G56" t="s">
+        <v>39</v>
+      </c>
+      <c r="H56">
+        <v>6614</v>
+      </c>
+      <c r="I56">
+        <v>1.2747200000000001</v>
+      </c>
+      <c r="J56">
+        <v>11.31553398</v>
+      </c>
+      <c r="K56">
+        <v>160</v>
+      </c>
+      <c r="L56" t="s">
+        <v>30</v>
+      </c>
+      <c r="M56">
+        <v>4662</v>
+      </c>
+      <c r="N56" t="s">
+        <v>104</v>
+      </c>
+      <c r="O56">
+        <v>8431</v>
+      </c>
+      <c r="P56">
+        <v>552.95931700000006</v>
+      </c>
+      <c r="Q56">
+        <v>412</v>
+      </c>
+      <c r="S56">
+        <v>11.315534</v>
+      </c>
+      <c r="T56">
+        <v>4.8867279999999997</v>
+      </c>
+      <c r="U56">
+        <v>468</v>
+      </c>
+      <c r="V56">
+        <v>5.5509430000000002</v>
+      </c>
+      <c r="W56">
+        <v>9.9615379999999991</v>
+      </c>
+      <c r="X56">
+        <v>399</v>
+      </c>
+      <c r="Y56">
+        <v>11.684210999999999</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C57" t="s">
+        <v>116</v>
+      </c>
+      <c r="D57" t="s">
+        <v>38</v>
+      </c>
+      <c r="E57" t="s">
+        <v>29</v>
+      </c>
+      <c r="F57">
+        <v>149</v>
+      </c>
+      <c r="G57" t="s">
+        <v>39</v>
+      </c>
+      <c r="H57">
+        <v>4548</v>
+      </c>
+      <c r="I57">
+        <v>1.416447</v>
+      </c>
+      <c r="J57">
+        <v>31.241610739999999</v>
+      </c>
+      <c r="K57">
+        <v>160</v>
+      </c>
+      <c r="L57" t="s">
+        <v>30</v>
+      </c>
+      <c r="M57">
+        <v>4655</v>
+      </c>
+      <c r="N57" t="s">
+        <v>104</v>
+      </c>
+      <c r="O57">
+        <v>6442</v>
+      </c>
+      <c r="P57">
+        <v>722.601677</v>
+      </c>
+      <c r="Q57">
+        <v>149</v>
+      </c>
+      <c r="S57">
+        <v>31.241610999999999</v>
+      </c>
+      <c r="T57">
+        <v>2.3129460000000002</v>
+      </c>
+      <c r="U57">
+        <v>174</v>
+      </c>
+      <c r="V57">
+        <v>2.701025</v>
+      </c>
+      <c r="W57">
+        <v>26.752873999999998</v>
+      </c>
+      <c r="X57">
+        <v>117</v>
+      </c>
+      <c r="Y57">
+        <v>39.786324999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" t="s">
+        <v>117</v>
+      </c>
+      <c r="D58" t="s">
+        <v>38</v>
+      </c>
+      <c r="E58" t="s">
+        <v>29</v>
+      </c>
+      <c r="F58">
+        <v>186</v>
+      </c>
+      <c r="G58" t="s">
+        <v>39</v>
+      </c>
+      <c r="H58">
+        <v>5769</v>
+      </c>
+      <c r="I58">
+        <v>1.547582</v>
+      </c>
+      <c r="J58">
+        <v>25.059139779999999</v>
+      </c>
+      <c r="K58">
+        <v>160</v>
+      </c>
+      <c r="L58" t="s">
+        <v>30</v>
+      </c>
+      <c r="M58">
+        <v>4661</v>
+      </c>
+      <c r="N58" t="s">
+        <v>104</v>
+      </c>
+      <c r="O58">
+        <v>8928</v>
+      </c>
+      <c r="P58">
+        <v>522.06541200000004</v>
+      </c>
+      <c r="Q58">
+        <v>186</v>
+      </c>
+      <c r="S58">
+        <v>25.059139999999999</v>
+      </c>
+      <c r="T58">
+        <v>2.0833330000000001</v>
+      </c>
+      <c r="U58">
+        <v>257</v>
+      </c>
+      <c r="V58">
+        <v>2.878584</v>
+      </c>
+      <c r="W58">
+        <v>18.136187</v>
+      </c>
+      <c r="X58">
+        <v>157</v>
+      </c>
+      <c r="Y58">
+        <v>29.687898000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" t="s">
+        <v>26</v>
+      </c>
+      <c r="C59" t="s">
+        <v>118</v>
+      </c>
+      <c r="D59" t="s">
+        <v>99</v>
+      </c>
+      <c r="E59" t="s">
+        <v>29</v>
+      </c>
+      <c r="F59">
+        <v>36</v>
+      </c>
+      <c r="G59" t="s">
+        <v>39</v>
+      </c>
+      <c r="H59">
+        <v>1112</v>
+      </c>
+      <c r="I59">
+        <v>1.190647</v>
+      </c>
+      <c r="J59">
+        <v>23.777777780000001</v>
+      </c>
+      <c r="K59">
+        <v>160</v>
+      </c>
+      <c r="L59" t="s">
+        <v>30</v>
+      </c>
+      <c r="M59">
+        <v>856</v>
+      </c>
+      <c r="N59" t="s">
+        <v>119</v>
+      </c>
+      <c r="O59">
+        <v>1324</v>
+      </c>
+      <c r="P59">
+        <v>646.52567999999997</v>
+      </c>
+      <c r="Q59">
+        <v>36</v>
+      </c>
+      <c r="S59">
+        <v>23.777778000000001</v>
+      </c>
+      <c r="T59">
+        <v>2.719033</v>
+      </c>
+      <c r="U59">
+        <v>40</v>
+      </c>
+      <c r="V59">
+        <v>3.0211480000000002</v>
+      </c>
+      <c r="W59">
+        <v>21.4</v>
+      </c>
+      <c r="X59">
+        <v>34</v>
+      </c>
+      <c r="Y59">
+        <v>25.176470999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C60" t="s">
+        <v>120</v>
+      </c>
+      <c r="D60" t="s">
+        <v>38</v>
+      </c>
+      <c r="E60" t="s">
+        <v>29</v>
+      </c>
+      <c r="F60">
+        <v>68</v>
+      </c>
+      <c r="G60" t="s">
+        <v>39</v>
+      </c>
+      <c r="H60">
+        <v>4648</v>
+      </c>
+      <c r="I60">
+        <v>1.5867039999999999</v>
+      </c>
+      <c r="J60">
+        <v>68.617647059999996</v>
+      </c>
+      <c r="K60">
+        <v>160</v>
+      </c>
+      <c r="L60" t="s">
+        <v>30</v>
+      </c>
+      <c r="M60">
+        <v>4666</v>
+      </c>
+      <c r="N60" t="s">
+        <v>104</v>
+      </c>
+      <c r="O60">
+        <v>7375</v>
+      </c>
+      <c r="P60">
+        <v>632.67796599999997</v>
+      </c>
+      <c r="Q60">
+        <v>68</v>
+      </c>
+      <c r="S60">
+        <v>68.617647000000005</v>
+      </c>
+      <c r="T60">
+        <v>0.92203400000000002</v>
+      </c>
+      <c r="U60">
+        <v>91</v>
+      </c>
+      <c r="V60">
+        <v>1.2338979999999999</v>
+      </c>
+      <c r="W60">
+        <v>51.274724999999997</v>
+      </c>
+      <c r="X60">
+        <v>11</v>
+      </c>
+      <c r="Y60">
+        <v>424.18181800000002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" t="s">
+        <v>121</v>
+      </c>
+      <c r="D61" t="s">
+        <v>38</v>
+      </c>
+      <c r="E61" t="s">
+        <v>29</v>
+      </c>
+      <c r="F61">
+        <v>491</v>
+      </c>
+      <c r="G61" t="s">
+        <v>39</v>
+      </c>
+      <c r="H61">
+        <v>5960</v>
+      </c>
+      <c r="I61">
+        <v>1.355537</v>
+      </c>
+      <c r="J61">
+        <v>9.5132382900000003</v>
+      </c>
+      <c r="K61">
+        <v>160</v>
+      </c>
+      <c r="L61" t="s">
+        <v>30</v>
+      </c>
+      <c r="M61">
+        <v>4671</v>
+      </c>
+      <c r="N61" t="s">
+        <v>104</v>
+      </c>
+      <c r="O61">
+        <v>8079</v>
+      </c>
+      <c r="P61">
+        <v>578.165615</v>
+      </c>
+      <c r="Q61">
+        <v>491</v>
+      </c>
+      <c r="S61">
+        <v>9.5132379999999994</v>
+      </c>
+      <c r="T61">
+        <v>6.0774850000000002</v>
+      </c>
+      <c r="U61">
+        <v>527</v>
+      </c>
+      <c r="V61">
+        <v>6.523085</v>
+      </c>
+      <c r="W61">
+        <v>8.8633780000000009</v>
+      </c>
+      <c r="X61">
+        <v>435</v>
+      </c>
+      <c r="Y61">
+        <v>10.737931</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62" t="s">
+        <v>122</v>
+      </c>
+      <c r="D62" t="s">
+        <v>28</v>
+      </c>
+      <c r="E62" t="s">
+        <v>29</v>
+      </c>
+      <c r="F62">
+        <v>511</v>
+      </c>
+      <c r="G62" t="s">
+        <v>39</v>
+      </c>
+      <c r="H62">
+        <v>4944</v>
+      </c>
+      <c r="I62">
+        <v>1.628641</v>
+      </c>
+      <c r="J62">
+        <v>9.1467710400000009</v>
+      </c>
+      <c r="K62">
+        <v>160</v>
+      </c>
+      <c r="L62" t="s">
+        <v>30</v>
+      </c>
+      <c r="M62">
+        <v>4674</v>
+      </c>
+      <c r="N62" t="s">
+        <v>104</v>
+      </c>
+      <c r="O62">
+        <v>8052</v>
+      </c>
+      <c r="P62">
+        <v>580.4769</v>
+      </c>
+      <c r="Q62">
+        <v>511</v>
+      </c>
+      <c r="S62">
+        <v>9.1467709999999993</v>
+      </c>
+      <c r="T62">
+        <v>6.3462490000000003</v>
+      </c>
+      <c r="U62">
+        <v>593</v>
+      </c>
+      <c r="V62">
+        <v>7.36463</v>
+      </c>
+      <c r="W62">
+        <v>7.8819559999999997</v>
+      </c>
+      <c r="X62">
+        <v>479</v>
+      </c>
+      <c r="Y62">
+        <v>9.7578289999999992</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>25</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63" t="s">
+        <v>77</v>
+      </c>
+      <c r="D63" t="s">
+        <v>28</v>
+      </c>
+      <c r="E63" t="s">
+        <v>29</v>
+      </c>
+      <c r="F63">
+        <v>79</v>
+      </c>
+      <c r="G63" t="s">
+        <v>39</v>
+      </c>
+      <c r="H63">
+        <v>2407</v>
+      </c>
+      <c r="I63">
+        <v>1.5803910000000001</v>
+      </c>
+      <c r="J63">
+        <v>57.367088610000003</v>
+      </c>
+      <c r="K63">
+        <v>160</v>
+      </c>
+      <c r="L63" t="s">
+        <v>30</v>
+      </c>
+      <c r="M63">
+        <v>4532</v>
+      </c>
+      <c r="N63" t="s">
+        <v>76</v>
+      </c>
+      <c r="O63">
+        <v>3804</v>
+      </c>
+      <c r="P63">
+        <v>1191.3774969999999</v>
+      </c>
+      <c r="Q63">
+        <v>79</v>
+      </c>
+      <c r="S63">
+        <v>57.367089</v>
+      </c>
+      <c r="T63">
+        <v>2.0767609999999999</v>
+      </c>
+      <c r="U63">
+        <v>87</v>
+      </c>
+      <c r="V63">
+        <v>2.2870659999999998</v>
+      </c>
+      <c r="W63">
+        <v>52.091954000000001</v>
+      </c>
+      <c r="X63">
+        <v>68</v>
+      </c>
+      <c r="Y63">
+        <v>66.647058999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>25</v>
+      </c>
+      <c r="B64" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" t="s">
+        <v>75</v>
+      </c>
+      <c r="D64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E64" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64">
+        <v>25</v>
+      </c>
+      <c r="G64" t="s">
+        <v>39</v>
+      </c>
+      <c r="H64">
+        <v>1751</v>
+      </c>
+      <c r="I64">
+        <v>1.7658480000000001</v>
+      </c>
+      <c r="J64">
+        <v>96.64</v>
+      </c>
+      <c r="K64">
+        <v>160</v>
+      </c>
+      <c r="L64" t="s">
+        <v>30</v>
+      </c>
+      <c r="M64">
+        <v>2416</v>
+      </c>
+      <c r="N64" t="s">
+        <v>76</v>
+      </c>
+      <c r="O64">
+        <v>3092</v>
+      </c>
+      <c r="P64">
+        <v>781.37128099999995</v>
+      </c>
+      <c r="Q64">
+        <v>25</v>
+      </c>
+      <c r="S64">
+        <v>96.64</v>
+      </c>
+      <c r="T64">
+        <v>0.80853799999999998</v>
+      </c>
+      <c r="U64">
+        <v>28</v>
+      </c>
+      <c r="V64">
+        <v>0.90556300000000001</v>
+      </c>
+      <c r="W64">
+        <v>86.285713999999999</v>
+      </c>
+      <c r="X64">
+        <v>21</v>
+      </c>
+      <c r="Y64">
+        <v>115.047619</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>25</v>
+      </c>
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65" t="s">
+        <v>123</v>
+      </c>
+      <c r="D65" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65">
+        <v>136</v>
+      </c>
+      <c r="G65" t="s">
+        <v>39</v>
+      </c>
+      <c r="H65">
+        <v>1960</v>
+      </c>
+      <c r="I65">
+        <v>1.4168369999999999</v>
+      </c>
+      <c r="J65">
+        <v>21.742647059999999</v>
+      </c>
+      <c r="K65">
+        <v>160</v>
+      </c>
+      <c r="L65" t="s">
+        <v>30</v>
+      </c>
+      <c r="M65">
+        <v>2957</v>
+      </c>
+      <c r="N65" t="s">
+        <v>46</v>
+      </c>
+      <c r="O65">
+        <v>2777</v>
+      </c>
+      <c r="P65">
+        <v>1064.8181489999999</v>
+      </c>
+      <c r="Q65">
+        <v>136</v>
+      </c>
+      <c r="S65">
+        <v>21.742647000000002</v>
+      </c>
+      <c r="T65">
+        <v>4.8973709999999997</v>
+      </c>
+      <c r="U65">
+        <v>148</v>
+      </c>
+      <c r="V65">
+        <v>5.3294920000000001</v>
+      </c>
+      <c r="W65">
+        <v>19.97973</v>
+      </c>
+      <c r="X65">
+        <v>124</v>
+      </c>
+      <c r="Y65">
+        <v>23.846774</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>25</v>
+      </c>
+      <c r="B66" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66" t="s">
+        <v>125</v>
+      </c>
+      <c r="D66" t="s">
+        <v>42</v>
+      </c>
+      <c r="E66" t="s">
+        <v>29</v>
+      </c>
+      <c r="F66">
+        <v>7</v>
+      </c>
+      <c r="G66" t="s">
+        <v>39</v>
+      </c>
+      <c r="H66">
+        <v>279</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="J66">
+        <v>27.85714286</v>
+      </c>
+      <c r="K66">
+        <v>160</v>
+      </c>
+      <c r="L66" t="s">
+        <v>30</v>
+      </c>
+      <c r="M66">
+        <v>195</v>
+      </c>
+      <c r="N66" t="s">
+        <v>41</v>
+      </c>
+      <c r="O66">
+        <v>279</v>
+      </c>
+      <c r="P66">
+        <v>698.92473099999995</v>
+      </c>
+      <c r="Q66">
+        <v>7</v>
+      </c>
+      <c r="S66">
+        <v>27.857143000000001</v>
+      </c>
+      <c r="T66">
+        <v>2.5089610000000002</v>
+      </c>
+      <c r="U66">
+        <v>8</v>
+      </c>
+      <c r="V66">
+        <v>2.8673839999999999</v>
+      </c>
+      <c r="W66">
+        <v>24.375</v>
+      </c>
+      <c r="X66">
+        <v>3</v>
+      </c>
+      <c r="Y66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>25</v>
+      </c>
+      <c r="B67" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67" t="s">
+        <v>125</v>
+      </c>
+      <c r="D67" t="s">
+        <v>42</v>
+      </c>
+      <c r="E67" t="s">
+        <v>29</v>
+      </c>
+      <c r="F67">
+        <v>6</v>
+      </c>
+      <c r="G67" t="s">
+        <v>39</v>
+      </c>
+      <c r="H67">
+        <v>267</v>
+      </c>
+      <c r="I67">
+        <v>1.108614</v>
+      </c>
+      <c r="J67">
+        <v>33.333333330000002</v>
+      </c>
+      <c r="K67">
+        <v>160</v>
+      </c>
+      <c r="L67" t="s">
+        <v>30</v>
+      </c>
+      <c r="M67">
+        <v>200</v>
+      </c>
+      <c r="N67" t="s">
+        <v>41</v>
+      </c>
+      <c r="O67">
+        <v>296</v>
+      </c>
+      <c r="P67">
+        <v>675.67567599999995</v>
+      </c>
+      <c r="Q67">
+        <v>6</v>
+      </c>
+      <c r="S67">
+        <v>33.333333000000003</v>
+      </c>
+      <c r="T67">
+        <v>2.0270269999999999</v>
+      </c>
+      <c r="U67">
+        <v>11</v>
+      </c>
+      <c r="V67">
+        <v>3.7162160000000002</v>
+      </c>
+      <c r="W67">
+        <v>18.181818</v>
+      </c>
+      <c r="X67">
+        <v>6</v>
+      </c>
+      <c r="Y67">
+        <v>33.333333000000003</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>25</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68" t="s">
+        <v>126</v>
+      </c>
+      <c r="D68" t="s">
+        <v>42</v>
+      </c>
+      <c r="E68" t="s">
+        <v>29</v>
+      </c>
+      <c r="F68">
+        <v>8</v>
+      </c>
+      <c r="G68" t="s">
+        <v>39</v>
+      </c>
+      <c r="H68">
+        <v>251</v>
+      </c>
+      <c r="I68">
+        <v>1.059761</v>
+      </c>
+      <c r="J68">
+        <v>29.75</v>
+      </c>
+      <c r="K68">
+        <v>160</v>
+      </c>
+      <c r="L68" t="s">
+        <v>30</v>
+      </c>
+      <c r="M68">
+        <v>238</v>
+      </c>
+      <c r="N68" t="s">
+        <v>41</v>
+      </c>
+      <c r="O68">
+        <v>266</v>
+      </c>
+      <c r="P68">
+        <v>894.73684200000002</v>
+      </c>
+      <c r="Q68">
+        <v>8</v>
+      </c>
+      <c r="S68">
+        <v>29.75</v>
+      </c>
+      <c r="T68">
+        <v>3.0075189999999998</v>
+      </c>
+      <c r="U68">
+        <v>9</v>
+      </c>
+      <c r="V68">
+        <v>3.3834590000000002</v>
+      </c>
+      <c r="W68">
+        <v>26.444444000000001</v>
+      </c>
+      <c r="X68">
+        <v>8</v>
+      </c>
+      <c r="Y68">
+        <v>29.75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>25</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69" t="s">
+        <v>127</v>
+      </c>
+      <c r="D69" t="s">
+        <v>42</v>
+      </c>
+      <c r="E69" t="s">
+        <v>29</v>
+      </c>
+      <c r="F69">
+        <v>8</v>
+      </c>
+      <c r="G69" t="s">
+        <v>39</v>
+      </c>
+      <c r="H69">
+        <v>276</v>
+      </c>
+      <c r="I69">
+        <v>1.0434779999999999</v>
+      </c>
+      <c r="J69">
+        <v>27.25</v>
+      </c>
+      <c r="K69">
+        <v>160</v>
+      </c>
+      <c r="L69" t="s">
+        <v>30</v>
+      </c>
+      <c r="M69">
+        <v>218</v>
+      </c>
+      <c r="N69" t="s">
+        <v>41</v>
+      </c>
+      <c r="O69">
+        <v>288</v>
+      </c>
+      <c r="P69">
+        <v>756.94444399999998</v>
+      </c>
+      <c r="Q69">
+        <v>8</v>
+      </c>
+      <c r="S69">
+        <v>27.25</v>
+      </c>
+      <c r="T69">
+        <v>2.7777780000000001</v>
+      </c>
+      <c r="U69">
+        <v>12</v>
+      </c>
+      <c r="V69">
+        <v>4.1666670000000003</v>
+      </c>
+      <c r="W69">
+        <v>18.166667</v>
+      </c>
+      <c r="X69">
+        <v>5</v>
+      </c>
+      <c r="Y69">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>25</v>
+      </c>
+      <c r="B70" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70" t="s">
+        <v>128</v>
+      </c>
+      <c r="D70" t="s">
+        <v>42</v>
+      </c>
+      <c r="E70" t="s">
+        <v>29</v>
+      </c>
+      <c r="F70">
+        <v>12</v>
+      </c>
+      <c r="G70" t="s">
+        <v>39</v>
+      </c>
+      <c r="H70">
+        <v>279</v>
+      </c>
+      <c r="I70">
+        <v>1.086022</v>
+      </c>
+      <c r="J70">
+        <v>17.75</v>
+      </c>
+      <c r="K70">
+        <v>160</v>
+      </c>
+      <c r="L70" t="s">
+        <v>30</v>
+      </c>
+      <c r="M70">
+        <v>213</v>
+      </c>
+      <c r="N70" t="s">
+        <v>41</v>
+      </c>
+      <c r="O70">
+        <v>303</v>
+      </c>
+      <c r="P70">
+        <v>702.97029699999996</v>
+      </c>
+      <c r="Q70">
+        <v>12</v>
+      </c>
+      <c r="S70">
+        <v>17.75</v>
+      </c>
+      <c r="T70">
+        <v>3.9603959999999998</v>
+      </c>
+      <c r="U70">
+        <v>13</v>
+      </c>
+      <c r="V70">
+        <v>4.2904289999999996</v>
+      </c>
+      <c r="W70">
+        <v>16.384615</v>
+      </c>
+      <c r="X70">
+        <v>8</v>
+      </c>
+      <c r="Y70">
+        <v>26.625</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>25</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71" t="s">
+        <v>129</v>
+      </c>
+      <c r="D71" t="s">
+        <v>28</v>
+      </c>
+      <c r="E71" t="s">
+        <v>29</v>
+      </c>
+      <c r="F71">
+        <v>8</v>
+      </c>
+      <c r="G71" t="s">
+        <v>39</v>
+      </c>
+      <c r="H71">
+        <v>253</v>
+      </c>
+      <c r="I71">
+        <v>1.075099</v>
+      </c>
+      <c r="J71">
+        <v>28.25</v>
+      </c>
+      <c r="K71">
+        <v>160</v>
+      </c>
+      <c r="L71" t="s">
+        <v>30</v>
+      </c>
+      <c r="M71">
+        <v>226</v>
+      </c>
+      <c r="N71" t="s">
+        <v>41</v>
+      </c>
+      <c r="O71">
+        <v>272</v>
+      </c>
+      <c r="P71">
+        <v>830.88235299999997</v>
+      </c>
+      <c r="Q71">
+        <v>8</v>
+      </c>
+      <c r="S71">
+        <v>28.25</v>
+      </c>
+      <c r="T71">
+        <v>2.941176</v>
+      </c>
+      <c r="U71">
+        <v>10</v>
+      </c>
+      <c r="V71">
+        <v>3.6764709999999998</v>
+      </c>
+      <c r="W71">
+        <v>22.6</v>
+      </c>
+      <c r="X71">
+        <v>6</v>
+      </c>
+      <c r="Y71">
+        <v>37.666666999999997</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>25</v>
+      </c>
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72" t="s">
+        <v>130</v>
+      </c>
+      <c r="D72" t="s">
+        <v>28</v>
+      </c>
+      <c r="E72" t="s">
+        <v>29</v>
+      </c>
+      <c r="F72">
+        <v>9</v>
+      </c>
+      <c r="G72" t="s">
+        <v>39</v>
+      </c>
+      <c r="H72">
+        <v>210</v>
+      </c>
+      <c r="I72">
+        <v>1.0809519999999999</v>
+      </c>
+      <c r="J72">
+        <v>26</v>
+      </c>
+      <c r="K72">
+        <v>160</v>
+      </c>
+      <c r="L72" t="s">
+        <v>30</v>
+      </c>
+      <c r="M72">
+        <v>234</v>
+      </c>
+      <c r="N72" t="s">
+        <v>41</v>
+      </c>
+      <c r="O72">
+        <v>227</v>
+      </c>
+      <c r="P72">
+        <v>1030.837004</v>
+      </c>
+      <c r="Q72">
+        <v>9</v>
+      </c>
+      <c r="S72">
+        <v>26</v>
+      </c>
+      <c r="T72">
+        <v>3.9647579999999998</v>
+      </c>
+      <c r="U72">
+        <v>10</v>
+      </c>
+      <c r="V72">
+        <v>4.4052860000000003</v>
+      </c>
+      <c r="W72">
+        <v>23.4</v>
+      </c>
+      <c r="X72">
+        <v>8</v>
+      </c>
+      <c r="Y72">
+        <v>29.25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>25</v>
+      </c>
+      <c r="B73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73" t="s">
+        <v>131</v>
+      </c>
+      <c r="D73" t="s">
+        <v>42</v>
+      </c>
+      <c r="E73" t="s">
+        <v>29</v>
+      </c>
+      <c r="F73">
+        <v>22</v>
+      </c>
+      <c r="G73" t="s">
+        <v>39</v>
+      </c>
+      <c r="H73">
+        <v>298</v>
+      </c>
+      <c r="I73">
+        <v>1.0738259999999999</v>
+      </c>
+      <c r="J73">
+        <v>10.5</v>
+      </c>
+      <c r="K73">
+        <v>160</v>
+      </c>
+      <c r="L73" t="s">
+        <v>30</v>
+      </c>
+      <c r="M73">
+        <v>231</v>
+      </c>
+      <c r="N73" t="s">
+        <v>132</v>
+      </c>
+      <c r="O73">
+        <v>320</v>
+      </c>
+      <c r="P73">
+        <v>721.875</v>
+      </c>
+      <c r="Q73">
+        <v>22</v>
+      </c>
+      <c r="S73">
+        <v>10.5</v>
+      </c>
+      <c r="T73">
+        <v>6.875</v>
+      </c>
+      <c r="U73">
+        <v>27</v>
+      </c>
+      <c r="V73">
+        <v>8.4375</v>
+      </c>
+      <c r="W73">
+        <v>8.5555559999999993</v>
+      </c>
+      <c r="X73">
+        <v>1</v>
+      </c>
+      <c r="Y73">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>25</v>
+      </c>
+      <c r="B74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74" t="s">
+        <v>133</v>
+      </c>
+      <c r="D74" t="s">
+        <v>42</v>
+      </c>
+      <c r="E74" t="s">
+        <v>29</v>
+      </c>
+      <c r="F74">
+        <v>4</v>
+      </c>
+      <c r="G74" t="s">
+        <v>39</v>
+      </c>
+      <c r="H74">
+        <v>222</v>
+      </c>
+      <c r="I74">
+        <v>1.09009</v>
+      </c>
+      <c r="J74">
+        <v>56.25</v>
+      </c>
+      <c r="K74">
+        <v>160</v>
+      </c>
+      <c r="L74" t="s">
+        <v>30</v>
+      </c>
+      <c r="M74">
+        <v>225</v>
+      </c>
+      <c r="N74" t="s">
+        <v>41</v>
+      </c>
+      <c r="O74">
+        <v>242</v>
+      </c>
+      <c r="P74">
+        <v>929.75206600000001</v>
+      </c>
+      <c r="Q74">
+        <v>4</v>
+      </c>
+      <c r="S74">
+        <v>56.25</v>
+      </c>
+      <c r="T74">
+        <v>1.6528929999999999</v>
+      </c>
+      <c r="U74">
+        <v>7</v>
+      </c>
+      <c r="V74">
+        <v>2.8925619999999999</v>
+      </c>
+      <c r="W74">
+        <v>32.142856999999999</v>
+      </c>
+      <c r="X74">
+        <v>5</v>
+      </c>
+      <c r="Y74">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>25</v>
+      </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75" t="s">
+        <v>134</v>
+      </c>
+      <c r="D75" t="s">
+        <v>42</v>
+      </c>
+      <c r="E75" t="s">
+        <v>29</v>
+      </c>
+      <c r="F75">
+        <v>4</v>
+      </c>
+      <c r="G75" t="s">
+        <v>39</v>
+      </c>
+      <c r="H75">
+        <v>215</v>
+      </c>
+      <c r="I75">
+        <v>1.065116</v>
+      </c>
+      <c r="J75">
+        <v>56.5</v>
+      </c>
+      <c r="K75">
+        <v>160</v>
+      </c>
+      <c r="L75" t="s">
+        <v>30</v>
+      </c>
+      <c r="M75">
+        <v>226</v>
+      </c>
+      <c r="N75" t="s">
+        <v>41</v>
+      </c>
+      <c r="O75">
+        <v>229</v>
+      </c>
+      <c r="P75">
+        <v>986.89956299999994</v>
+      </c>
+      <c r="Q75">
+        <v>4</v>
+      </c>
+      <c r="S75">
+        <v>56.5</v>
+      </c>
+      <c r="T75">
+        <v>1.7467250000000001</v>
+      </c>
+      <c r="U75">
+        <v>5</v>
+      </c>
+      <c r="V75">
+        <v>2.1834060000000002</v>
+      </c>
+      <c r="W75">
+        <v>45.2</v>
+      </c>
+      <c r="X75">
+        <v>3</v>
+      </c>
+      <c r="Y75">
+        <v>75.333332999999996</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>25</v>
+      </c>
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76" t="s">
+        <v>135</v>
+      </c>
+      <c r="D76" t="s">
+        <v>42</v>
+      </c>
+      <c r="E76" t="s">
+        <v>29</v>
+      </c>
+      <c r="F76">
+        <v>13</v>
+      </c>
+      <c r="G76" t="s">
+        <v>39</v>
+      </c>
+      <c r="H76">
+        <v>315</v>
+      </c>
+      <c r="I76">
+        <v>1.022222</v>
+      </c>
+      <c r="J76">
+        <v>16.23076923</v>
+      </c>
+      <c r="K76">
+        <v>160</v>
+      </c>
+      <c r="L76" t="s">
+        <v>30</v>
+      </c>
+      <c r="M76">
+        <v>211</v>
+      </c>
+      <c r="N76" t="s">
+        <v>41</v>
+      </c>
+      <c r="O76">
+        <v>322</v>
+      </c>
+      <c r="P76">
+        <v>655.27950299999998</v>
+      </c>
+      <c r="Q76">
+        <v>13</v>
+      </c>
+      <c r="S76">
+        <v>16.230768999999999</v>
+      </c>
+      <c r="T76">
+        <v>4.0372669999999999</v>
+      </c>
+      <c r="U76">
+        <v>15</v>
+      </c>
+      <c r="V76">
+        <v>4.658385</v>
+      </c>
+      <c r="W76">
+        <v>14.066667000000001</v>
+      </c>
+      <c r="X76">
+        <v>13</v>
+      </c>
+      <c r="Y76">
+        <v>16.230768999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>25</v>
+      </c>
+      <c r="B77" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77" t="s">
+        <v>136</v>
+      </c>
+      <c r="D77" t="s">
+        <v>42</v>
+      </c>
+      <c r="E77" t="s">
+        <v>29</v>
+      </c>
+      <c r="F77">
+        <v>14</v>
+      </c>
+      <c r="G77" t="s">
+        <v>39</v>
+      </c>
+      <c r="H77">
+        <v>202</v>
+      </c>
+      <c r="I77">
+        <v>1.029703</v>
+      </c>
+      <c r="J77">
+        <v>11.57142857</v>
+      </c>
+      <c r="K77">
+        <v>160</v>
+      </c>
+      <c r="L77" t="s">
+        <v>30</v>
+      </c>
+      <c r="M77">
+        <v>162</v>
+      </c>
+      <c r="N77" t="s">
+        <v>41</v>
+      </c>
+      <c r="O77">
+        <v>208</v>
+      </c>
+      <c r="P77">
+        <v>778.84615399999996</v>
+      </c>
+      <c r="Q77">
+        <v>14</v>
+      </c>
+      <c r="S77">
+        <v>11.571429</v>
+      </c>
+      <c r="T77">
+        <v>6.7307689999999996</v>
+      </c>
+      <c r="U77">
+        <v>14</v>
+      </c>
+      <c r="V77">
+        <v>6.7307689999999996</v>
+      </c>
+      <c r="W77">
+        <v>11.571429</v>
+      </c>
+      <c r="X77">
+        <v>13</v>
+      </c>
+      <c r="Y77">
+        <v>12.461537999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>25</v>
+      </c>
+      <c r="B78" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78" t="s">
+        <v>137</v>
+      </c>
+      <c r="D78" t="s">
+        <v>42</v>
+      </c>
+      <c r="E78" t="s">
+        <v>29</v>
+      </c>
+      <c r="F78">
+        <v>3</v>
+      </c>
+      <c r="G78" t="s">
+        <v>39</v>
+      </c>
+      <c r="H78">
+        <v>172</v>
+      </c>
+      <c r="I78">
+        <v>1.011628</v>
+      </c>
+      <c r="J78">
+        <v>55.666666669999998</v>
+      </c>
+      <c r="K78">
+        <v>160</v>
+      </c>
+      <c r="L78" t="s">
+        <v>30</v>
+      </c>
+      <c r="M78">
+        <v>167</v>
+      </c>
+      <c r="N78" t="s">
+        <v>41</v>
+      </c>
+      <c r="O78">
+        <v>174</v>
+      </c>
+      <c r="P78">
+        <v>959.77011500000003</v>
+      </c>
+      <c r="Q78">
+        <v>3</v>
+      </c>
+      <c r="S78">
+        <v>55.666666999999997</v>
+      </c>
+      <c r="T78">
+        <v>1.7241379999999999</v>
+      </c>
+      <c r="U78">
+        <v>4</v>
+      </c>
+      <c r="V78">
+        <v>2.298851</v>
+      </c>
+      <c r="W78">
+        <v>41.75</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>25</v>
+      </c>
+      <c r="B79" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79" t="s">
+        <v>138</v>
+      </c>
+      <c r="D79" t="s">
+        <v>42</v>
+      </c>
+      <c r="E79" t="s">
+        <v>29</v>
+      </c>
+      <c r="F79">
+        <v>24</v>
+      </c>
+      <c r="G79" t="s">
+        <v>39</v>
+      </c>
+      <c r="H79">
+        <v>338</v>
+      </c>
+      <c r="I79">
+        <v>1.0443789999999999</v>
+      </c>
+      <c r="J79">
+        <v>9.4583333300000003</v>
+      </c>
+      <c r="K79">
+        <v>160</v>
+      </c>
+      <c r="L79" t="s">
+        <v>30</v>
+      </c>
+      <c r="M79">
+        <v>227</v>
+      </c>
+      <c r="N79" t="s">
+        <v>41</v>
+      </c>
+      <c r="O79">
+        <v>353</v>
+      </c>
+      <c r="P79">
+        <v>643.05948999999998</v>
+      </c>
+      <c r="Q79">
+        <v>24</v>
+      </c>
+      <c r="S79">
+        <v>9.4583329999999997</v>
+      </c>
+      <c r="T79">
+        <v>6.7988670000000004</v>
+      </c>
+      <c r="U79">
+        <v>27</v>
+      </c>
+      <c r="V79">
+        <v>7.6487249999999998</v>
+      </c>
+      <c r="W79">
+        <v>8.4074069999999992</v>
+      </c>
+      <c r="X79">
+        <v>21</v>
+      </c>
+      <c r="Y79">
+        <v>10.809524</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>25</v>
+      </c>
+      <c r="B80" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" t="s">
+        <v>139</v>
+      </c>
+      <c r="D80" t="s">
+        <v>42</v>
+      </c>
+      <c r="E80" t="s">
+        <v>29</v>
+      </c>
+      <c r="F80">
+        <v>5</v>
+      </c>
+      <c r="G80" t="s">
+        <v>39</v>
+      </c>
+      <c r="H80">
+        <v>181</v>
+      </c>
+      <c r="I80">
+        <v>1.071823</v>
+      </c>
+      <c r="J80">
+        <v>33.6</v>
+      </c>
+      <c r="K80">
+        <v>160</v>
+      </c>
+      <c r="L80" t="s">
+        <v>30</v>
+      </c>
+      <c r="M80">
+        <v>168</v>
+      </c>
+      <c r="N80" t="s">
+        <v>41</v>
+      </c>
+      <c r="O80">
+        <v>194</v>
+      </c>
+      <c r="P80">
+        <v>865.97938099999999</v>
+      </c>
+      <c r="Q80">
+        <v>5</v>
+      </c>
+      <c r="S80">
+        <v>33.6</v>
+      </c>
+      <c r="T80">
+        <v>2.5773199999999998</v>
+      </c>
+      <c r="U80">
+        <v>7</v>
+      </c>
+      <c r="V80">
+        <v>3.608247</v>
+      </c>
+      <c r="W80">
+        <v>24</v>
+      </c>
+      <c r="X80">
+        <v>5</v>
+      </c>
+      <c r="Y80">
+        <v>33.6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>25</v>
+      </c>
+      <c r="B81" t="s">
+        <v>26</v>
+      </c>
+      <c r="C81" t="s">
+        <v>140</v>
+      </c>
+      <c r="D81" t="s">
+        <v>42</v>
+      </c>
+      <c r="E81" t="s">
+        <v>29</v>
+      </c>
+      <c r="F81">
+        <v>2</v>
+      </c>
+      <c r="G81" t="s">
+        <v>39</v>
+      </c>
+      <c r="H81">
+        <v>154</v>
+      </c>
+      <c r="I81">
+        <v>1.0129870000000001</v>
+      </c>
+      <c r="J81">
+        <v>76.5</v>
+      </c>
+      <c r="K81">
+        <v>160</v>
+      </c>
+      <c r="L81" t="s">
+        <v>30</v>
+      </c>
+      <c r="M81">
+        <v>153</v>
+      </c>
+      <c r="N81" t="s">
+        <v>41</v>
+      </c>
+      <c r="O81">
+        <v>156</v>
+      </c>
+      <c r="P81">
+        <v>980.76923099999999</v>
+      </c>
+      <c r="Q81">
+        <v>2</v>
+      </c>
+      <c r="S81">
+        <v>76.5</v>
+      </c>
+      <c r="T81">
+        <v>1.2820510000000001</v>
+      </c>
+      <c r="U81">
+        <v>3</v>
+      </c>
+      <c r="V81">
+        <v>1.9230769999999999</v>
+      </c>
+      <c r="W81">
+        <v>51</v>
+      </c>
+      <c r="X81">
+        <v>1</v>
+      </c>
+      <c r="Y81">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>25</v>
+      </c>
+      <c r="B82" t="s">
+        <v>26</v>
+      </c>
+      <c r="C82" t="s">
+        <v>141</v>
+      </c>
+      <c r="D82" t="s">
+        <v>28</v>
+      </c>
+      <c r="E82" t="s">
+        <v>29</v>
+      </c>
+      <c r="F82">
+        <v>6</v>
+      </c>
+      <c r="G82" t="s">
+        <v>39</v>
+      </c>
+      <c r="H82">
+        <v>120</v>
+      </c>
+      <c r="I82">
+        <v>1.05</v>
+      </c>
+      <c r="J82">
+        <v>27.5</v>
+      </c>
+      <c r="K82">
+        <v>160</v>
+      </c>
+      <c r="L82" t="s">
+        <v>30</v>
+      </c>
+      <c r="M82">
+        <v>165</v>
+      </c>
+      <c r="N82" t="s">
+        <v>41</v>
+      </c>
+      <c r="O82">
+        <v>126</v>
+      </c>
+      <c r="P82">
+        <v>1309.5238099999999</v>
+      </c>
+      <c r="Q82">
+        <v>6</v>
+      </c>
+      <c r="S82">
+        <v>27.5</v>
+      </c>
+      <c r="T82">
+        <v>4.7619049999999996</v>
+      </c>
+      <c r="U82">
+        <v>7</v>
+      </c>
+      <c r="V82">
+        <v>5.5555560000000002</v>
+      </c>
+      <c r="W82">
+        <v>23.571428999999998</v>
+      </c>
+      <c r="X82">
+        <v>5</v>
+      </c>
+      <c r="Y82">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>25</v>
+      </c>
+      <c r="B83" t="s">
+        <v>26</v>
+      </c>
+      <c r="C83" t="s">
+        <v>142</v>
+      </c>
+      <c r="D83" t="s">
+        <v>28</v>
+      </c>
+      <c r="E83" t="s">
+        <v>29</v>
+      </c>
+      <c r="F83">
+        <v>5</v>
+      </c>
+      <c r="G83" t="s">
+        <v>39</v>
+      </c>
+      <c r="H83">
+        <v>102</v>
+      </c>
+      <c r="I83">
+        <v>1.0392159999999999</v>
+      </c>
+      <c r="J83">
+        <v>40.6</v>
+      </c>
+      <c r="K83">
+        <v>160</v>
+      </c>
+      <c r="L83" t="s">
+        <v>30</v>
+      </c>
+      <c r="M83">
+        <v>203</v>
+      </c>
+      <c r="N83" t="s">
+        <v>41</v>
+      </c>
+      <c r="O83">
+        <v>106</v>
+      </c>
+      <c r="P83">
+        <v>1915.0943400000001</v>
+      </c>
+      <c r="Q83">
+        <v>5</v>
+      </c>
+      <c r="S83">
+        <v>40.6</v>
+      </c>
+      <c r="T83">
+        <v>4.7169809999999996</v>
+      </c>
+      <c r="U83">
+        <v>5</v>
+      </c>
+      <c r="V83">
+        <v>4.7169809999999996</v>
+      </c>
+      <c r="W83">
+        <v>40.6</v>
+      </c>
+      <c r="X83">
+        <v>4</v>
+      </c>
+      <c r="Y83">
+        <v>50.75</v>
+      </c>
+    </row>
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>25</v>
+      </c>
+      <c r="B84" t="s">
+        <v>26</v>
+      </c>
+      <c r="C84" t="s">
+        <v>143</v>
+      </c>
+      <c r="D84" t="s">
+        <v>42</v>
+      </c>
+      <c r="E84" t="s">
+        <v>29</v>
+      </c>
+      <c r="F84">
+        <v>2</v>
+      </c>
+      <c r="G84" t="s">
+        <v>39</v>
+      </c>
+      <c r="H84">
+        <v>126</v>
+      </c>
+      <c r="I84">
+        <v>1.0238100000000001</v>
+      </c>
+      <c r="J84">
+        <v>97.5</v>
+      </c>
+      <c r="K84">
+        <v>160</v>
+      </c>
+      <c r="L84" t="s">
+        <v>30</v>
+      </c>
+      <c r="M84">
+        <v>195</v>
+      </c>
+      <c r="N84" t="s">
+        <v>41</v>
+      </c>
+      <c r="O84">
+        <v>129</v>
+      </c>
+      <c r="P84">
+        <v>1511.6279070000001</v>
+      </c>
+      <c r="Q84">
+        <v>2</v>
+      </c>
+      <c r="S84">
+        <v>97.5</v>
+      </c>
+      <c r="T84">
+        <v>1.5503880000000001</v>
+      </c>
+      <c r="U84">
+        <v>3</v>
+      </c>
+      <c r="V84">
+        <v>2.3255810000000001</v>
+      </c>
+      <c r="W84">
+        <v>65</v>
+      </c>
+      <c r="X84">
+        <v>2</v>
+      </c>
+      <c r="Y84">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>25</v>
+      </c>
+      <c r="B85" t="s">
+        <v>26</v>
+      </c>
+      <c r="C85" t="s">
+        <v>144</v>
+      </c>
+      <c r="D85" t="s">
+        <v>42</v>
+      </c>
+      <c r="E85" t="s">
+        <v>29</v>
+      </c>
+      <c r="F85">
+        <v>3</v>
+      </c>
+      <c r="G85" t="s">
+        <v>39</v>
+      </c>
+      <c r="H85">
+        <v>135</v>
+      </c>
+      <c r="I85">
+        <v>1.0444439999999999</v>
+      </c>
+      <c r="J85">
+        <v>59.333333330000002</v>
+      </c>
+      <c r="K85">
+        <v>160</v>
+      </c>
+      <c r="L85" t="s">
+        <v>30</v>
+      </c>
+      <c r="M85">
+        <v>178</v>
+      </c>
+      <c r="N85" t="s">
+        <v>41</v>
+      </c>
+      <c r="O85">
+        <v>141</v>
+      </c>
+      <c r="P85">
+        <v>1262.4113480000001</v>
+      </c>
+      <c r="Q85">
+        <v>3</v>
+      </c>
+      <c r="S85">
+        <v>59.333333000000003</v>
+      </c>
+      <c r="T85">
+        <v>2.1276600000000001</v>
+      </c>
+      <c r="U85">
+        <v>3</v>
+      </c>
+      <c r="V85">
+        <v>2.1276600000000001</v>
+      </c>
+      <c r="W85">
+        <v>59.333333000000003</v>
+      </c>
+      <c r="X85">
+        <v>1</v>
+      </c>
+      <c r="Y85">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>25</v>
+      </c>
+      <c r="B86" t="s">
+        <v>26</v>
+      </c>
+      <c r="C86" t="s">
+        <v>145</v>
+      </c>
+      <c r="D86" t="s">
+        <v>42</v>
+      </c>
+      <c r="E86" t="s">
+        <v>29</v>
+      </c>
+      <c r="F86">
+        <v>4</v>
+      </c>
+      <c r="G86" t="s">
+        <v>39</v>
+      </c>
+      <c r="H86">
+        <v>184</v>
+      </c>
+      <c r="I86">
+        <v>1.0326090000000001</v>
+      </c>
+      <c r="J86">
+        <v>39.25</v>
+      </c>
+      <c r="K86">
+        <v>160</v>
+      </c>
+      <c r="L86" t="s">
+        <v>30</v>
+      </c>
+      <c r="M86">
+        <v>157</v>
+      </c>
+      <c r="N86" t="s">
+        <v>41</v>
+      </c>
+      <c r="O86">
+        <v>190</v>
+      </c>
+      <c r="P86">
+        <v>826.315789</v>
+      </c>
+      <c r="Q86">
+        <v>4</v>
+      </c>
+      <c r="S86">
+        <v>39.25</v>
+      </c>
+      <c r="T86">
+        <v>2.1052629999999999</v>
+      </c>
+      <c r="U86">
+        <v>4</v>
+      </c>
+      <c r="V86">
+        <v>2.1052629999999999</v>
+      </c>
+      <c r="W86">
+        <v>39.25</v>
+      </c>
+      <c r="X86">
+        <v>4</v>
+      </c>
+      <c r="Y86">
+        <v>39.25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>25</v>
+      </c>
+      <c r="B87" t="s">
+        <v>26</v>
+      </c>
+      <c r="C87" t="s">
+        <v>146</v>
+      </c>
+      <c r="D87" t="s">
+        <v>42</v>
+      </c>
+      <c r="E87" t="s">
+        <v>29</v>
+      </c>
+      <c r="F87">
+        <v>3</v>
+      </c>
+      <c r="G87" t="s">
+        <v>39</v>
+      </c>
+      <c r="H87">
+        <v>272</v>
+      </c>
+      <c r="I87">
+        <v>1.0441180000000001</v>
+      </c>
+      <c r="J87">
+        <v>54.666666669999998</v>
+      </c>
+      <c r="K87">
+        <v>160</v>
+      </c>
+      <c r="L87" t="s">
+        <v>30</v>
+      </c>
+      <c r="M87">
+        <v>164</v>
+      </c>
+      <c r="N87" t="s">
+        <v>41</v>
+      </c>
+      <c r="O87">
+        <v>284</v>
+      </c>
+      <c r="P87">
+        <v>577.464789</v>
+      </c>
+      <c r="Q87">
+        <v>3</v>
+      </c>
+      <c r="S87">
+        <v>54.666666999999997</v>
+      </c>
+      <c r="T87">
+        <v>1.056338</v>
+      </c>
+      <c r="U87">
+        <v>6</v>
+      </c>
+      <c r="V87">
+        <v>2.112676</v>
+      </c>
+      <c r="W87">
+        <v>27.333333</v>
+      </c>
+      <c r="X87">
+        <v>4</v>
+      </c>
+      <c r="Y87">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>25</v>
+      </c>
+      <c r="B88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C88" t="s">
+        <v>147</v>
+      </c>
+      <c r="D88" t="s">
+        <v>42</v>
+      </c>
+      <c r="E88" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88">
+        <v>3</v>
+      </c>
+      <c r="G88" t="s">
+        <v>39</v>
+      </c>
+      <c r="H88">
+        <v>117</v>
+      </c>
+      <c r="I88">
+        <v>1.068376</v>
+      </c>
+      <c r="J88">
+        <v>39.333333330000002</v>
+      </c>
+      <c r="K88">
+        <v>160</v>
+      </c>
+      <c r="L88" t="s">
+        <v>30</v>
+      </c>
+      <c r="M88">
+        <v>118</v>
+      </c>
+      <c r="N88" t="s">
+        <v>148</v>
+      </c>
+      <c r="O88">
+        <v>125</v>
+      </c>
+      <c r="P88">
+        <v>944</v>
+      </c>
+      <c r="Q88">
+        <v>3</v>
+      </c>
+      <c r="S88">
+        <v>39.333333000000003</v>
+      </c>
+      <c r="T88">
+        <v>2.4</v>
+      </c>
+      <c r="U88">
+        <v>4</v>
+      </c>
+      <c r="V88">
+        <v>3.2</v>
+      </c>
+      <c r="W88">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>25</v>
+      </c>
+      <c r="B89" t="s">
+        <v>26</v>
+      </c>
+      <c r="C89" t="s">
+        <v>149</v>
+      </c>
+      <c r="D89" t="s">
+        <v>42</v>
+      </c>
+      <c r="E89" t="s">
+        <v>29</v>
+      </c>
+      <c r="F89">
+        <v>8</v>
+      </c>
+      <c r="G89" t="s">
+        <v>39</v>
+      </c>
+      <c r="H89">
+        <v>159</v>
+      </c>
+      <c r="I89">
+        <v>1.031447</v>
+      </c>
+      <c r="J89">
+        <v>15.125</v>
+      </c>
+      <c r="K89">
+        <v>160</v>
+      </c>
+      <c r="L89" t="s">
+        <v>30</v>
+      </c>
+      <c r="M89">
+        <v>121</v>
+      </c>
+      <c r="N89" t="s">
+        <v>148</v>
+      </c>
+      <c r="O89">
+        <v>164</v>
+      </c>
+      <c r="P89">
+        <v>737.80487800000003</v>
+      </c>
+      <c r="Q89">
+        <v>8</v>
+      </c>
+      <c r="S89">
+        <v>15.125</v>
+      </c>
+      <c r="T89">
+        <v>4.8780489999999999</v>
+      </c>
+      <c r="U89">
+        <v>10</v>
+      </c>
+      <c r="V89">
+        <v>6.0975609999999998</v>
+      </c>
+      <c r="W89">
+        <v>12.1</v>
+      </c>
+      <c r="X89">
+        <v>1</v>
+      </c>
+      <c r="Y89">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>25</v>
+      </c>
+      <c r="B90" t="s">
+        <v>26</v>
+      </c>
+      <c r="C90" t="s">
+        <v>150</v>
+      </c>
+      <c r="D90" t="s">
+        <v>42</v>
+      </c>
+      <c r="E90" t="s">
+        <v>29</v>
+      </c>
+      <c r="F90">
+        <v>9</v>
+      </c>
+      <c r="G90" t="s">
+        <v>39</v>
+      </c>
+      <c r="H90">
+        <v>110</v>
+      </c>
+      <c r="I90">
+        <v>1.0363640000000001</v>
+      </c>
+      <c r="J90">
+        <v>9.6666666699999997</v>
+      </c>
+      <c r="K90">
+        <v>160</v>
+      </c>
+      <c r="L90" t="s">
+        <v>30</v>
+      </c>
+      <c r="M90">
+        <v>87</v>
+      </c>
+      <c r="N90" t="s">
+        <v>148</v>
+      </c>
+      <c r="O90">
+        <v>114</v>
+      </c>
+      <c r="P90">
+        <v>763.15789500000005</v>
+      </c>
+      <c r="Q90">
+        <v>9</v>
+      </c>
+      <c r="S90">
+        <v>9.6666670000000003</v>
+      </c>
+      <c r="T90">
+        <v>7.8947370000000001</v>
+      </c>
+      <c r="U90">
+        <v>14</v>
+      </c>
+      <c r="V90">
+        <v>12.280702</v>
+      </c>
+      <c r="W90">
+        <v>6.2142860000000004</v>
+      </c>
+    </row>
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" t="s">
+        <v>26</v>
+      </c>
+      <c r="C91" t="s">
+        <v>151</v>
+      </c>
+      <c r="D91" t="s">
+        <v>38</v>
+      </c>
+      <c r="E91" t="s">
+        <v>29</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>160</v>
+      </c>
+      <c r="L91" t="s">
+        <v>30</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91" t="s">
+        <v>152</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+      <c r="U91">
+        <v>0</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
